--- a/data/trans_dic/P55$privada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 28,17</t>
+          <t>5,22; 27,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,94</t>
+          <t>0,0; 19,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,1; 27,25</t>
+          <t>3,06; 26,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,4; 29,53</t>
+          <t>12,72; 29,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,64; 35,14</t>
+          <t>10,82; 34,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 22,64</t>
+          <t>5,39; 22,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,55; 30,14</t>
+          <t>7,87; 29,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 23,27</t>
+          <t>12,32; 23,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 27,55</t>
+          <t>10,14; 27,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 17,68</t>
+          <t>4,62; 17,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,35; 24,7</t>
+          <t>7,44; 24,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 23,87</t>
+          <t>14,37; 23,64</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 18,55</t>
+          <t>1,99; 18,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 30,68</t>
+          <t>7,06; 30,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 29,93</t>
+          <t>8,15; 29,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 20,14</t>
+          <t>4,19; 20,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 24,47</t>
+          <t>6,72; 25,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 22,05</t>
+          <t>7,3; 21,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,67</t>
+          <t>2,83; 17,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,81; 23,44</t>
+          <t>11,66; 23,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,94; 19,95</t>
+          <t>6,86; 19,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 22,12</t>
+          <t>8,92; 21,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 17,21</t>
+          <t>5,73; 16,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 19,52</t>
+          <t>10,62; 19,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,3</t>
+          <t>0,0; 27,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 27,01</t>
+          <t>0,0; 26,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 32,75</t>
+          <t>6,99; 34,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 43,12</t>
+          <t>17,12; 45,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 27,65</t>
+          <t>6,07; 28,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 34,83</t>
+          <t>9,69; 35,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 26,58</t>
+          <t>11,24; 26,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,16; 31,01</t>
+          <t>11,95; 32,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 23,64</t>
+          <t>6,03; 23,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 27,77</t>
+          <t>10,03; 29,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,93; 24,81</t>
+          <t>11,91; 25,39</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 46,12</t>
+          <t>11,34; 49,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 36,58</t>
+          <t>9,96; 38,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 33,77</t>
+          <t>7,14; 34,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 25,71</t>
+          <t>8,16; 25,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,27; 35,29</t>
+          <t>15,88; 37,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,25; 38,34</t>
+          <t>17,26; 37,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 33,4</t>
+          <t>10,66; 32,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,1; 27,68</t>
+          <t>14,41; 27,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,85; 35,77</t>
+          <t>17,72; 35,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,91; 33,5</t>
+          <t>16,03; 33,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 29,36</t>
+          <t>12,05; 29,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,45; 24,46</t>
+          <t>14,51; 24,33</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,22</t>
+          <t>7,09; 18,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,25</t>
+          <t>8,83; 20,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 21,58</t>
+          <t>9,42; 21,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,06; 20,57</t>
+          <t>11,88; 21,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 27,85</t>
+          <t>16,67; 27,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,9</t>
+          <t>12,45; 21,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 21,93</t>
+          <t>11,48; 22,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,54; 21,52</t>
+          <t>15,33; 21,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,51</t>
+          <t>14,56; 22,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,34; 20,02</t>
+          <t>12,48; 19,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 20,04</t>
+          <t>11,69; 19,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,04; 20,29</t>
+          <t>15,28; 20,15</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1794; 9544</t>
+          <t>1769; 9357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5837</t>
+          <t>0; 6489</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>861; 7570</t>
+          <t>850; 7331</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6156; 14656</t>
+          <t>6312; 14642</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4765; 15738</t>
+          <t>4846; 15559</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3143; 13814</t>
+          <t>3287; 13975</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4542; 18124</t>
+          <t>4733; 17466</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9954; 18541</t>
+          <t>9816; 18466</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8268; 21671</t>
+          <t>7980; 21859</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4813; 16536</t>
+          <t>4321; 16100</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6466; 21716</t>
+          <t>6543; 21333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17964; 30864</t>
+          <t>18586; 30563</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>964; 8909</t>
+          <t>958; 8679</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3271; 14008</t>
+          <t>3223; 13765</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3325; 12244</t>
+          <t>3334; 12205</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1670; 7794</t>
+          <t>1619; 7948</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4460; 16558</t>
+          <t>4546; 16982</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6535; 19476</t>
+          <t>6446; 19393</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2095; 11269</t>
+          <t>2175; 13472</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10154; 20159</t>
+          <t>10029; 19840</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8034; 23085</t>
+          <t>7943; 22349</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11867; 29643</t>
+          <t>11953; 29320</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6666; 20263</t>
+          <t>6748; 19418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13581; 24336</t>
+          <t>13236; 24692</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1864</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7629</t>
+          <t>0; 7646</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>844; 6283</t>
+          <t>0; 6222</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1674; 8360</t>
+          <t>1784; 8816</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7558; 20034</t>
+          <t>7953; 20961</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2334; 14356</t>
+          <t>3152; 14801</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5652; 17961</t>
+          <t>5000; 18058</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6542; 15498</t>
+          <t>6556; 15193</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7595; 21101</t>
+          <t>8132; 21980</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4552; 18875</t>
+          <t>4819; 18557</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6967; 20779</t>
+          <t>7509; 21768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10002; 20796</t>
+          <t>9982; 21283</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2579; 10657</t>
+          <t>2620; 11492</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4019; 14645</t>
+          <t>3988; 15267</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2293; 9966</t>
+          <t>2106; 10320</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3655; 11114</t>
+          <t>3526; 10938</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10992; 25408</t>
+          <t>11431; 26658</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12720; 30009</t>
+          <t>13508; 29447</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8657; 26324</t>
+          <t>8405; 25327</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15741; 28859</t>
+          <t>15024; 28291</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16025; 34014</t>
+          <t>16847; 33828</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20003; 39629</t>
+          <t>18969; 39086</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13504; 31808</t>
+          <t>13055; 32267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21311; 36078</t>
+          <t>21409; 35889</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9267; 23059</t>
+          <t>8978; 22788</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12129; 29601</t>
+          <t>12907; 30208</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11525; 26215</t>
+          <t>11444; 26023</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18949; 32316</t>
+          <t>18667; 33011</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38331; 64313</t>
+          <t>38499; 63705</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>35222; 61208</t>
+          <t>34794; 61431</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30009; 58628</t>
+          <t>30705; 59190</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>51023; 70644</t>
+          <t>50322; 71059</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51325; 80466</t>
+          <t>52046; 79541</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52537; 85224</t>
+          <t>53131; 84693</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46339; 77914</t>
+          <t>45469; 75345</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>72994; 98478</t>
+          <t>74166; 97772</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$privada-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 27,62</t>
+          <t>5,2; 28,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,94</t>
+          <t>0,0; 19,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 26,39</t>
+          <t>2,99; 24,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,72; 29,5</t>
+          <t>12,8; 30,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,82; 34,74</t>
+          <t>10,99; 36,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 22,91</t>
+          <t>5,25; 23,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 29,04</t>
+          <t>7,46; 28,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,18</t>
+          <t>12,53; 23,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 27,79</t>
+          <t>10,26; 28,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 17,21</t>
+          <t>4,87; 17,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 24,27</t>
+          <t>8,05; 24,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,37; 23,64</t>
+          <t>14,19; 23,71</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 18,07</t>
+          <t>2,01; 18,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,06; 30,15</t>
+          <t>7,19; 29,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,15; 29,83</t>
+          <t>8,16; 30,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 20,54</t>
+          <t>4,62; 21,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 25,09</t>
+          <t>7,92; 25,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 21,95</t>
+          <t>7,17; 21,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,83; 17,53</t>
+          <t>2,69; 15,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,66; 23,07</t>
+          <t>11,8; 23,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,86; 19,32</t>
+          <t>6,6; 18,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,92; 21,88</t>
+          <t>9,42; 21,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 16,49</t>
+          <t>5,76; 17,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,62; 19,8</t>
+          <t>10,65; 19,92</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -1002,57 +1002,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,37</t>
+          <t>0,0; 28,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,75</t>
+          <t>3,66; 27,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 34,54</t>
+          <t>7,04; 33,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,12; 45,11</t>
+          <t>18,02; 44,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 28,51</t>
+          <t>5,13; 27,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,69; 35,02</t>
+          <t>10,07; 34,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,24; 26,05</t>
+          <t>11,13; 26,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,95; 32,3</t>
+          <t>11,62; 31,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 23,24</t>
+          <t>6,35; 23,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,03; 29,09</t>
+          <t>10,4; 28,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 25,39</t>
+          <t>11,04; 24,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 49,73</t>
+          <t>11,35; 48,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,96; 38,13</t>
+          <t>9,82; 35,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 34,97</t>
+          <t>7,7; 34,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,16; 25,3</t>
+          <t>8,37; 24,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>15,88; 37,03</t>
+          <t>14,82; 35,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,26; 37,62</t>
+          <t>16,89; 38,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,66; 32,14</t>
+          <t>11,99; 32,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,41; 27,13</t>
+          <t>14,97; 28,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,72; 35,57</t>
+          <t>17,36; 34,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,03; 33,04</t>
+          <t>16,84; 32,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 29,79</t>
+          <t>12,32; 30,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,51; 24,33</t>
+          <t>14,31; 25,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,0</t>
+          <t>7,1; 17,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 20,67</t>
+          <t>8,83; 20,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,42; 21,43</t>
+          <t>9,13; 21,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,88; 21,02</t>
+          <t>11,83; 20,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,59</t>
+          <t>16,56; 27,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,45; 21,98</t>
+          <t>12,38; 21,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,48; 22,14</t>
+          <t>11,5; 21,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,33; 21,65</t>
+          <t>15,5; 21,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,25</t>
+          <t>14,77; 22,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,48; 19,9</t>
+          <t>11,98; 19,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,69; 19,38</t>
+          <t>11,91; 19,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 20,15</t>
+          <t>15,13; 20,27</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14832</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>25851</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1769; 9357</t>
+          <t>1762; 9560</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6489</t>
+          <t>0; 6231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>850; 7331</t>
+          <t>832; 6679</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6312; 14642</t>
+          <t>6786; 16336</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4846; 15559</t>
+          <t>4922; 16193</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3287; 13975</t>
+          <t>3204; 14079</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4733; 17466</t>
+          <t>4485; 17362</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9816; 18466</t>
+          <t>10632; 20044</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7980; 21859</t>
+          <t>8070; 22213</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4321; 16100</t>
+          <t>4556; 16288</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6543; 21333</t>
+          <t>7079; 21401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18586; 30563</t>
+          <t>19565; 32693</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>20255</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>958; 8679</t>
+          <t>963; 8807</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3223; 13765</t>
+          <t>3284; 13456</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3334; 12205</t>
+          <t>3337; 12275</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1619; 7948</t>
+          <t>1934; 9067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4546; 16982</t>
+          <t>5361; 17346</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6446; 19393</t>
+          <t>6336; 19225</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2175; 13472</t>
+          <t>2066; 11938</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10029; 19840</t>
+          <t>11170; 21800</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7943; 22349</t>
+          <t>7635; 21864</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11953; 29320</t>
+          <t>12622; 29107</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6748; 19418</t>
+          <t>6788; 20209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13236; 24692</t>
+          <t>14539; 27191</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>11422</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>16258</t>
         </is>
       </c>
     </row>
@@ -2066,57 +2066,57 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7646</t>
+          <t>0; 7896</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6222</t>
+          <t>852; 6367</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1784; 8816</t>
+          <t>2091; 9874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7953; 20961</t>
+          <t>8375; 20719</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3152; 14801</t>
+          <t>2664; 14240</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5000; 18058</t>
+          <t>5194; 17949</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6556; 15193</t>
+          <t>7222; 16907</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8132; 21980</t>
+          <t>7903; 21635</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4819; 18557</t>
+          <t>5074; 18775</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7509; 21768</t>
+          <t>7785; 21624</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9982; 21283</t>
+          <t>10447; 23639</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6704</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>23504</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>27984</t>
+          <t>30207</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2620; 11492</t>
+          <t>2623; 11276</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3988; 15267</t>
+          <t>3931; 14329</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2106; 10320</t>
+          <t>2271; 10218</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3526; 10938</t>
+          <t>3732; 11091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11431; 26658</t>
+          <t>10669; 25690</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13508; 29447</t>
+          <t>13224; 29891</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8405; 25327</t>
+          <t>9449; 25891</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15024; 28291</t>
+          <t>16890; 31912</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16847; 33828</t>
+          <t>16509; 33225</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18969; 39086</t>
+          <t>19926; 38286</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13055; 32267</t>
+          <t>13343; 32536</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>21409; 35889</t>
+          <t>22528; 39522</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>92571</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8978; 22788</t>
+          <t>8993; 22591</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12907; 30208</t>
+          <t>12905; 30593</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11444; 26023</t>
+          <t>11091; 25643</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18667; 33011</t>
+          <t>20002; 35469</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38499; 63705</t>
+          <t>38243; 63953</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34794; 61431</t>
+          <t>34608; 60147</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30705; 59190</t>
+          <t>30741; 57077</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>50322; 71059</t>
+          <t>55390; 77733</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>52046; 79541</t>
+          <t>52795; 80466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>53131; 84693</t>
+          <t>50978; 83270</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45469; 75345</t>
+          <t>46327; 76812</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>74166; 97772</t>
+          <t>79630; 106687</t>
         </is>
       </c>
     </row>
